--- a/data/input/Housekeeping_Dados.xlsx
+++ b/data/input/Housekeeping_Dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emariasantos/Desktop/Horários dos alojamentos/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4913C527-08AA-B546-AA02-E444E195CD0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11315CFB-15A2-794E-864E-A379EF100DCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="21800" windowHeight="11620" activeTab="4" xr2:uid="{F0287AD0-DDE7-4F0D-A1F8-C2319EEDC301}"/>
   </bookViews>
@@ -4110,7 +4110,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4" s="4">
         <v>6</v>
@@ -4120,15 +4120,9 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="7">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4">
-        <v>5</v>
-      </c>
-      <c r="C5" s="6">
-        <v>1</v>
-      </c>
+      <c r="A5" s="7"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="6"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="7"/>
@@ -4413,23 +4407,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="6623f56b-56d8-4afd-a862-c76771b81233" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100CF923B54B0E5054B8CFD22B8369F6D81" ma:contentTypeVersion="5" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="1e31ba1d2c63c7fdfdcbeba4d93011b6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="6623f56b-56d8-4afd-a862-c76771b81233" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8808e44b28f29d6edb360e0bbd209acc" ns3:_="">
     <xsd:import namespace="6623f56b-56d8-4afd-a862-c76771b81233"/>
@@ -4579,10 +4556,37 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="6623f56b-56d8-4afd-a862-c76771b81233" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34F9FCC5-A4BC-4105-B7D3-0FB7E15531A3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85DD04AB-95C3-4BAA-86CD-00C5E9654C1A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="6623f56b-56d8-4afd-a862-c76771b81233"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4604,19 +4608,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85DD04AB-95C3-4BAA-86CD-00C5E9654C1A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34F9FCC5-A4BC-4105-B7D3-0FB7E15531A3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="6623f56b-56d8-4afd-a862-c76771b81233"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>